--- a/user feedback/combined.xlsx
+++ b/user feedback/combined.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ak/Desktop/Final/Submission_VC_Agents/user feedback/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D688A170-5E0E-F04A-A674-CDD8E063D616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{715FBB2A-2E04-7943-B3B8-A623C57E4D78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="27040" windowHeight="15700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="89">
   <si>
     <t>Rater ID</t>
   </si>
@@ -279,28 +279,6 @@
     <t>8-10</t>
   </si>
   <si>
-    <t xml:space="preserve">The Memo can be enhanced with KPI metrics of the EquityBee platform (if they were disclosed or publicly available). For example, number of customers, number of investors, repeat investors etc. </t>
-  </si>
-  <si>
-    <t>The Memo can benefit from a more frequent use of diagrams, tables and other visuals in place of long texts</t>
-  </si>
-  <si>
-    <t>Please see comments earlier</t>
-  </si>
-  <si>
-    <t>The Memo provides a complete overview of the potential investment target and acts as a valuable to commence investment research. 
-The Memo even covers such areas as patenting and the technological stack.</t>
-  </si>
-  <si>
-    <t>The Memo needs a bit of work on its overall presentation to enhance readibility, decrease reading time and use less plain text</t>
-  </si>
-  <si>
-    <t>4-6 hours</t>
-  </si>
-  <si>
-    <t>Comments to previous feedback</t>
-  </si>
-  <si>
     <t>As a summary of company/transaction</t>
   </si>
   <si>
@@ -317,6 +295,12 @@
   </si>
   <si>
     <t>Avg.</t>
+  </si>
+  <si>
+    <t>Good structure and language</t>
+  </si>
+  <si>
+    <t>Too broad and vague, lacks specifics (most of conclusions could be applicable to any startup), many repetitions, lack of visual component</t>
   </si>
 </sst>
 </file>
@@ -418,7 +402,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -440,9 +424,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -467,12 +448,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1030,248 +1006,317 @@
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
     </row>
-    <row r="7" spans="1:19" ht="96" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A7" s="7">
+        <v>4</v>
+      </c>
+      <c r="B7" s="7">
+        <v>3</v>
+      </c>
+      <c r="C7" s="7">
+        <v>3</v>
+      </c>
+      <c r="D7" s="7">
+        <v>3</v>
+      </c>
+      <c r="E7" s="7">
+        <v>4</v>
+      </c>
+      <c r="F7" s="7">
+        <v>5</v>
+      </c>
+      <c r="G7" s="7">
+        <v>3</v>
+      </c>
+      <c r="H7" s="7">
+        <v>5</v>
+      </c>
+      <c r="I7" s="7">
+        <v>3</v>
+      </c>
+      <c r="J7" s="7">
+        <v>5</v>
+      </c>
+      <c r="K7" s="7">
+        <v>5</v>
+      </c>
+      <c r="L7" s="7">
+        <v>3</v>
+      </c>
+      <c r="M7" s="7">
+        <v>1</v>
+      </c>
+      <c r="N7" s="7">
+        <v>3</v>
+      </c>
+      <c r="O7" s="7">
+        <v>3</v>
+      </c>
+      <c r="P7" s="7">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="R7" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="S7" s="9" t="s">
-        <v>86</v>
-      </c>
+      <c r="R7" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="S7" s="7"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
-        <v>4</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="18"/>
-      <c r="R8" s="18"/>
-      <c r="S8" s="19"/>
-    </row>
-    <row r="9" spans="1:19" ht="32" x14ac:dyDescent="0.2">
-      <c r="A9" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="B9" s="11">
-        <v>5</v>
-      </c>
-      <c r="C9" s="11">
-        <v>4</v>
-      </c>
-      <c r="D9" s="11">
-        <v>4</v>
-      </c>
-      <c r="E9" s="11">
-        <v>3</v>
-      </c>
-      <c r="F9" s="11">
-        <v>3</v>
-      </c>
-      <c r="G9" s="11">
-        <v>4</v>
-      </c>
-      <c r="H9" s="11">
-        <v>5</v>
-      </c>
-      <c r="I9" s="11">
-        <v>3</v>
-      </c>
-      <c r="J9" s="11">
-        <v>4</v>
-      </c>
-      <c r="K9" s="11">
-        <v>3</v>
-      </c>
-      <c r="L9" s="11">
-        <v>3</v>
-      </c>
-      <c r="M9" s="11">
-        <v>3</v>
-      </c>
-      <c r="N9" s="11">
-        <v>4</v>
-      </c>
-      <c r="O9" s="11">
-        <v>2</v>
-      </c>
-      <c r="P9" s="11">
-        <v>2</v>
-      </c>
-      <c r="Q9" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="R9" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="S9" s="13" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="48" x14ac:dyDescent="0.2">
-      <c r="A10" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="B10" s="11">
-        <v>2</v>
-      </c>
-      <c r="C10" s="11">
-        <v>2</v>
-      </c>
-      <c r="D10" s="11">
-        <v>3</v>
-      </c>
-      <c r="E10" s="11">
-        <v>1</v>
-      </c>
-      <c r="F10" s="11">
-        <v>2</v>
-      </c>
-      <c r="G10" s="11">
-        <v>3</v>
-      </c>
-      <c r="H10" s="11">
-        <v>4</v>
-      </c>
-      <c r="I10" s="11">
-        <v>2</v>
-      </c>
-      <c r="J10" s="11">
-        <v>3</v>
-      </c>
-      <c r="K10" s="11">
-        <v>2</v>
-      </c>
-      <c r="L10" s="11">
-        <v>2</v>
-      </c>
-      <c r="M10" s="11">
-        <v>3</v>
-      </c>
-      <c r="N10" s="11">
-        <v>3</v>
-      </c>
-      <c r="O10" s="11">
-        <v>2</v>
-      </c>
-      <c r="P10" s="11">
-        <v>2</v>
-      </c>
-      <c r="Q10" s="14"/>
-      <c r="R10" s="14"/>
-      <c r="S10" s="15"/>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A11" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B11" s="17">
+        <v>5</v>
+      </c>
+      <c r="B8" s="16">
         <f>AVERAGE(B9:B10)</f>
         <v>3.5</v>
       </c>
-      <c r="C11" s="17">
-        <f t="shared" ref="C11:P11" si="0">AVERAGE(C9:C10)</f>
-        <v>3</v>
-      </c>
-      <c r="D11" s="17">
+      <c r="C8" s="16">
+        <f t="shared" ref="C8:P8" si="0">AVERAGE(C9:C10)</f>
+        <v>3</v>
+      </c>
+      <c r="D8" s="16">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E8" s="16">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F8" s="16">
         <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G8" s="16">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="H11" s="17">
+      <c r="H8" s="16">
         <f t="shared" si="0"/>
         <v>4.5</v>
       </c>
-      <c r="I11" s="17">
+      <c r="I8" s="16">
         <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
-      <c r="J11" s="17">
+      <c r="J8" s="16">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="K11" s="17">
+      <c r="K8" s="16">
         <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
-      <c r="L11" s="17">
+      <c r="L8" s="16">
         <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
-      <c r="M11" s="17">
+      <c r="M8" s="16">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="N11" s="17">
+      <c r="N8" s="16">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="O11" s="17">
+      <c r="O8" s="16">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="P11" s="17">
+      <c r="P8" s="16">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="Q11" s="16"/>
-      <c r="R11" s="16"/>
-      <c r="S11" s="16"/>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="17"/>
+      <c r="S8" s="17"/>
+    </row>
+    <row r="9" spans="1:19" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="10">
+        <v>5</v>
+      </c>
+      <c r="C9" s="10">
+        <v>4</v>
+      </c>
+      <c r="D9" s="10">
+        <v>4</v>
+      </c>
+      <c r="E9" s="10">
+        <v>3</v>
+      </c>
+      <c r="F9" s="10">
+        <v>3</v>
+      </c>
+      <c r="G9" s="10">
+        <v>4</v>
+      </c>
+      <c r="H9" s="10">
+        <v>5</v>
+      </c>
+      <c r="I9" s="10">
+        <v>3</v>
+      </c>
+      <c r="J9" s="10">
+        <v>4</v>
+      </c>
+      <c r="K9" s="10">
+        <v>3</v>
+      </c>
+      <c r="L9" s="10">
+        <v>3</v>
+      </c>
+      <c r="M9" s="10">
+        <v>3</v>
+      </c>
+      <c r="N9" s="10">
+        <v>4</v>
+      </c>
+      <c r="O9" s="10">
+        <v>2</v>
+      </c>
+      <c r="P9" s="10">
+        <v>2</v>
+      </c>
+      <c r="Q9" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="R9" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S9" s="12" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="48" x14ac:dyDescent="0.2">
+      <c r="A10" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" s="10">
+        <v>2</v>
+      </c>
+      <c r="C10" s="10">
+        <v>2</v>
+      </c>
+      <c r="D10" s="10">
+        <v>3</v>
+      </c>
+      <c r="E10" s="10">
+        <v>1</v>
+      </c>
+      <c r="F10" s="10">
+        <v>2</v>
+      </c>
+      <c r="G10" s="10">
+        <v>3</v>
+      </c>
+      <c r="H10" s="10">
+        <v>4</v>
+      </c>
+      <c r="I10" s="10">
+        <v>2</v>
+      </c>
+      <c r="J10" s="10">
+        <v>3</v>
+      </c>
+      <c r="K10" s="10">
+        <v>2</v>
+      </c>
+      <c r="L10" s="10">
+        <v>2</v>
+      </c>
+      <c r="M10" s="10">
+        <v>3</v>
+      </c>
+      <c r="N10" s="10">
+        <v>3</v>
+      </c>
+      <c r="O10" s="10">
+        <v>2</v>
+      </c>
+      <c r="P10" s="10">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="14"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A11" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" s="16">
+        <f>AVERAGE(B9:B10)</f>
+        <v>3.5</v>
+      </c>
+      <c r="C11" s="16">
+        <f t="shared" ref="C11:P11" si="1">AVERAGE(C9:C10)</f>
+        <v>3</v>
+      </c>
+      <c r="D11" s="16">
+        <f t="shared" si="1"/>
+        <v>3.5</v>
+      </c>
+      <c r="E11" s="16">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="F11" s="16">
+        <f t="shared" si="1"/>
+        <v>2.5</v>
+      </c>
+      <c r="G11" s="16">
+        <f t="shared" si="1"/>
+        <v>3.5</v>
+      </c>
+      <c r="H11" s="16">
+        <f t="shared" si="1"/>
+        <v>4.5</v>
+      </c>
+      <c r="I11" s="16">
+        <f t="shared" si="1"/>
+        <v>2.5</v>
+      </c>
+      <c r="J11" s="16">
+        <f t="shared" si="1"/>
+        <v>3.5</v>
+      </c>
+      <c r="K11" s="16">
+        <f t="shared" si="1"/>
+        <v>2.5</v>
+      </c>
+      <c r="L11" s="16">
+        <f t="shared" si="1"/>
+        <v>2.5</v>
+      </c>
+      <c r="M11" s="16">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="N11" s="16">
+        <f t="shared" si="1"/>
+        <v>3.5</v>
+      </c>
+      <c r="O11" s="16">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="P11" s="16">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="Q11" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="R11" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="S11" s="15"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A12" s="7">
-        <v>5</v>
-      </c>
+      <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1287,15 +1332,17 @@
       <c r="N12" s="7"/>
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
-      <c r="Q12" s="7"/>
-      <c r="R12" s="7"/>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="13"/>
       <c r="S12" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="R9:R10"/>
     <mergeCell ref="S9:S10"/>
     <mergeCell ref="Q9:Q10"/>
+    <mergeCell ref="Q11:Q12"/>
+    <mergeCell ref="R11:R12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/user feedback/combined.xlsx
+++ b/user feedback/combined.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ak/Desktop/Final/Submission_VC_Agents/user feedback/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{715FBB2A-2E04-7943-B3B8-A623C57E4D78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{269971EB-1BB5-F44F-9510-E9B5E165FB44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="700" windowWidth="27040" windowHeight="15700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="820" windowWidth="27040" windowHeight="15700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ratings" sheetId="1" r:id="rId1"/>
     <sheet name="Instructions" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,10 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="89">
-  <si>
-    <t>Rater ID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="89">
   <si>
     <t>Overall usefullness 1-5</t>
   </si>
@@ -279,21 +276,12 @@
     <t>8-10</t>
   </si>
   <si>
-    <t>As a summary of company/transaction</t>
-  </si>
-  <si>
     <t>As a disclaimer, I am judging the strengths of this memo as if it were a summary of the company/transaction. I would 100% use this automatically generated memo to screen deals and as support as I write my investment memo. I also like that it transparently shows uncertainty ("may", "seems", etc.) and states where additional diligence/research is needed as opposed to hallucinating. The memo covers a comprehensive list of sections--though I'm not sure if these were preset search conditions/sections.</t>
   </si>
   <si>
     <t>As a disclaimer, I am judging the strengths of this memo as if it were an initial draft of a memo I would bring for Deal Review (prior to IC). The main issue for is that the business model and tech of the company was not clearly and granularly explained (though I understand the sources may have been limited). Beyond that, the competitors were adjacent (non-direct), which does not allow for an apples-to-apples comparison--which, in turn, lowers the quality of the risk analysis. Risk section is missing key concepts related to stock option valuation, counterparty dispute/failure, disintermediation, macro (down-round, slowdowns, etc.), concentration, etc., which should be mentioned with a caveat that DD is required. For the exit strat section, the next level would be providing potential names that would acquire the company--or at least types of companies in detail.</t>
   </si>
   <si>
-    <t>3-4 hours</t>
-  </si>
-  <si>
-    <t>As an initial draft of a memo I would bring for Deal Review (prior to IC)</t>
-  </si>
-  <si>
     <t>Avg.</t>
   </si>
   <si>
@@ -301,6 +289,21 @@
   </si>
   <si>
     <t>Too broad and vague, lacks specifics (most of conclusions could be applicable to any startup), many repetitions, lack of visual component</t>
+  </si>
+  <si>
+    <t>1. Good language and logics of narrative.
+2. Well-structured and consequential.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Pretty noticable portion of obviously formalized, pattern-based overwhelming text. Seem to exploit too many exended descriptional instruments, while lacking stressing on figures and their more comprehensive explanation.
+2. Points 4. and 5. are excessively repeating already mentioned basics of the topic.
+3. Point 14. sounds like copy&amp;paste: scarce and not tailored to the case in hand. </t>
+  </si>
+  <si>
+    <t>6+ hours, provided that all necessary factual data is available or easily accessible.</t>
+  </si>
+  <si>
+    <t>§</t>
   </si>
 </sst>
 </file>
@@ -310,7 +313,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -334,19 +337,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="4">
@@ -402,7 +412,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -416,39 +426,49 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -753,596 +773,544 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:S12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A3:AK11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="28.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="32.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="30" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="35.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="52.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="22" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="52.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="235.1640625" customWidth="1"/>
-    <col min="18" max="18" width="72.5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="102.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="28.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="32.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.83203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="35.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="52.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="52.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="235.1640625" style="6" customWidth="1"/>
+    <col min="18" max="18" width="72.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="102.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="8.83203125" style="6"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A3" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="6" t="s">
+      <c r="F3" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="J3" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="J3" s="6" t="s">
+      <c r="K3" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="L3" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="M3" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="N3" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="O3" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="P3" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="Q3" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="R3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="S3" s="6" t="s">
+      <c r="S3" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A4" s="18">
+        <v>1</v>
+      </c>
+      <c r="B4" s="18">
+        <v>5</v>
+      </c>
+      <c r="C4" s="18">
+        <v>5</v>
+      </c>
+      <c r="D4" s="18">
+        <v>5</v>
+      </c>
+      <c r="E4" s="18">
+        <v>5</v>
+      </c>
+      <c r="F4" s="18">
+        <v>5</v>
+      </c>
+      <c r="G4" s="18">
+        <v>5</v>
+      </c>
+      <c r="H4" s="18">
+        <v>5</v>
+      </c>
+      <c r="I4" s="18">
+        <v>5</v>
+      </c>
+      <c r="J4" s="18">
+        <v>5</v>
+      </c>
+      <c r="K4" s="18">
+        <v>5</v>
+      </c>
+      <c r="L4" s="18">
+        <v>5</v>
+      </c>
+      <c r="M4" s="18">
+        <v>5</v>
+      </c>
+      <c r="N4" s="18">
+        <v>5</v>
+      </c>
+      <c r="O4" s="18">
+        <v>5</v>
+      </c>
+      <c r="P4" s="18">
+        <v>5</v>
+      </c>
+      <c r="Q4" s="18" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A4" s="7">
-        <v>1</v>
-      </c>
-      <c r="B4" s="7">
-        <v>5</v>
-      </c>
-      <c r="C4" s="7">
-        <v>5</v>
-      </c>
-      <c r="D4" s="7">
-        <v>5</v>
-      </c>
-      <c r="E4" s="7">
-        <v>5</v>
-      </c>
-      <c r="F4" s="7">
-        <v>5</v>
-      </c>
-      <c r="G4" s="7">
-        <v>5</v>
-      </c>
-      <c r="H4" s="7">
-        <v>5</v>
-      </c>
-      <c r="I4" s="7">
-        <v>5</v>
-      </c>
-      <c r="J4" s="7">
-        <v>5</v>
-      </c>
-      <c r="K4" s="7">
-        <v>5</v>
-      </c>
-      <c r="L4" s="7">
-        <v>5</v>
-      </c>
-      <c r="M4" s="7">
-        <v>5</v>
-      </c>
-      <c r="N4" s="7">
-        <v>5</v>
-      </c>
-      <c r="O4" s="7">
-        <v>5</v>
-      </c>
-      <c r="P4" s="7">
-        <v>5</v>
-      </c>
-      <c r="Q4" s="7" t="s">
+      <c r="R4" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S4" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="R4" s="7" t="s">
+    </row>
+    <row r="5" spans="1:37" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="18">
+        <v>2</v>
+      </c>
+      <c r="B5" s="18">
+        <v>4</v>
+      </c>
+      <c r="C5" s="18">
+        <v>4</v>
+      </c>
+      <c r="D5" s="18">
+        <v>4</v>
+      </c>
+      <c r="E5" s="18">
+        <v>4</v>
+      </c>
+      <c r="F5" s="18">
+        <v>4</v>
+      </c>
+      <c r="G5" s="18">
+        <v>4</v>
+      </c>
+      <c r="H5" s="18">
+        <v>4</v>
+      </c>
+      <c r="I5" s="18">
+        <v>4</v>
+      </c>
+      <c r="J5" s="18">
+        <v>4</v>
+      </c>
+      <c r="K5" s="18">
+        <v>4</v>
+      </c>
+      <c r="L5" s="18">
+        <v>4</v>
+      </c>
+      <c r="M5" s="18">
+        <v>4</v>
+      </c>
+      <c r="N5" s="18">
+        <v>4</v>
+      </c>
+      <c r="O5" s="18">
+        <v>4</v>
+      </c>
+      <c r="P5" s="18">
+        <v>4</v>
+      </c>
+      <c r="Q5" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="S4" s="7" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="7">
-        <v>2</v>
-      </c>
-      <c r="B5" s="7">
-        <v>4</v>
-      </c>
-      <c r="C5" s="7">
-        <v>4</v>
-      </c>
-      <c r="D5" s="7">
-        <v>4</v>
-      </c>
-      <c r="E5" s="7">
-        <v>4</v>
-      </c>
-      <c r="F5" s="7">
-        <v>4</v>
-      </c>
-      <c r="G5" s="7">
-        <v>4</v>
-      </c>
-      <c r="H5" s="7">
-        <v>4</v>
-      </c>
-      <c r="I5" s="7">
-        <v>4</v>
-      </c>
-      <c r="J5" s="7">
-        <v>4</v>
-      </c>
-      <c r="K5" s="7">
-        <v>4</v>
-      </c>
-      <c r="L5" s="7">
-        <v>4</v>
-      </c>
-      <c r="M5" s="7">
-        <v>4</v>
-      </c>
-      <c r="N5" s="7">
-        <v>4</v>
-      </c>
-      <c r="O5" s="7">
-        <v>4</v>
-      </c>
-      <c r="P5" s="7">
-        <v>4</v>
-      </c>
-      <c r="Q5" s="7" t="s">
+      <c r="R5" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="R5" s="5" t="s">
+      <c r="S5" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="S5" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A6" s="7">
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A6" s="18">
         <v>3</v>
       </c>
-      <c r="B6" s="7">
-        <v>5</v>
-      </c>
-      <c r="C6" s="7">
-        <v>4</v>
-      </c>
-      <c r="D6" s="7">
-        <v>5</v>
-      </c>
-      <c r="E6" s="7">
-        <v>5</v>
-      </c>
-      <c r="F6" s="7">
-        <v>5</v>
-      </c>
-      <c r="G6" s="7">
-        <v>5</v>
-      </c>
-      <c r="H6" s="7">
-        <v>4</v>
-      </c>
-      <c r="I6" s="7">
-        <v>5</v>
-      </c>
-      <c r="J6" s="7">
-        <v>5</v>
-      </c>
-      <c r="K6" s="7">
-        <v>5</v>
-      </c>
-      <c r="L6" s="7">
-        <v>5</v>
-      </c>
-      <c r="M6" s="7">
-        <v>5</v>
-      </c>
-      <c r="N6" s="7">
-        <v>4</v>
-      </c>
-      <c r="O6" s="7">
-        <v>5</v>
-      </c>
-      <c r="P6" s="7">
-        <v>5</v>
-      </c>
-      <c r="Q6" s="7"/>
+      <c r="B6" s="18">
+        <v>5</v>
+      </c>
+      <c r="C6" s="18">
+        <v>4</v>
+      </c>
+      <c r="D6" s="18">
+        <v>5</v>
+      </c>
+      <c r="E6" s="18">
+        <v>5</v>
+      </c>
+      <c r="F6" s="18">
+        <v>5</v>
+      </c>
+      <c r="G6" s="18">
+        <v>5</v>
+      </c>
+      <c r="H6" s="18">
+        <v>4</v>
+      </c>
+      <c r="I6" s="18">
+        <v>5</v>
+      </c>
+      <c r="J6" s="18">
+        <v>5</v>
+      </c>
+      <c r="K6" s="18">
+        <v>5</v>
+      </c>
+      <c r="L6" s="18">
+        <v>5</v>
+      </c>
+      <c r="M6" s="18">
+        <v>5</v>
+      </c>
+      <c r="N6" s="18">
+        <v>4</v>
+      </c>
+      <c r="O6" s="18">
+        <v>5</v>
+      </c>
+      <c r="P6" s="18">
+        <v>5</v>
+      </c>
+      <c r="Q6" s="18"/>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A7" s="7">
-        <v>4</v>
-      </c>
-      <c r="B7" s="7">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A7" s="18">
+        <v>4</v>
+      </c>
+      <c r="B7" s="18">
         <v>3</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="18">
         <v>3</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="18">
         <v>3</v>
       </c>
-      <c r="E7" s="7">
-        <v>4</v>
-      </c>
-      <c r="F7" s="7">
-        <v>5</v>
-      </c>
-      <c r="G7" s="7">
+      <c r="E7" s="18">
+        <v>4</v>
+      </c>
+      <c r="F7" s="18">
+        <v>5</v>
+      </c>
+      <c r="G7" s="18">
         <v>3</v>
       </c>
-      <c r="H7" s="7">
-        <v>5</v>
-      </c>
-      <c r="I7" s="7">
+      <c r="H7" s="18">
+        <v>5</v>
+      </c>
+      <c r="I7" s="18">
         <v>3</v>
       </c>
-      <c r="J7" s="7">
-        <v>5</v>
-      </c>
-      <c r="K7" s="7">
-        <v>5</v>
-      </c>
-      <c r="L7" s="7">
+      <c r="J7" s="18">
+        <v>5</v>
+      </c>
+      <c r="K7" s="18">
+        <v>5</v>
+      </c>
+      <c r="L7" s="18">
         <v>3</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="18">
         <v>1</v>
       </c>
-      <c r="N7" s="7">
+      <c r="N7" s="18">
         <v>3</v>
       </c>
-      <c r="O7" s="7">
+      <c r="O7" s="18">
         <v>3</v>
       </c>
-      <c r="P7" s="7">
+      <c r="P7" s="18">
         <v>3</v>
       </c>
-      <c r="Q7" s="7" t="s">
+      <c r="Q7" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="R7" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="S7" s="7"/>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A8" s="18">
+        <v>5</v>
+      </c>
+      <c r="B8" s="19">
+        <v>3.5</v>
+      </c>
+      <c r="C8" s="19">
+        <v>3</v>
+      </c>
+      <c r="D8" s="19">
+        <v>3.5</v>
+      </c>
+      <c r="E8" s="19">
+        <v>2</v>
+      </c>
+      <c r="F8" s="19">
+        <v>2.5</v>
+      </c>
+      <c r="G8" s="19">
+        <v>3.5</v>
+      </c>
+      <c r="H8" s="19">
+        <v>4.5</v>
+      </c>
+      <c r="I8" s="19">
+        <v>2.5</v>
+      </c>
+      <c r="J8" s="19">
+        <v>3.5</v>
+      </c>
+      <c r="K8" s="19">
+        <v>2.5</v>
+      </c>
+      <c r="L8" s="19">
+        <v>2.5</v>
+      </c>
+      <c r="M8" s="19">
+        <v>3</v>
+      </c>
+      <c r="N8" s="19">
+        <v>3.5</v>
+      </c>
+      <c r="O8" s="19">
+        <v>2</v>
+      </c>
+      <c r="P8" s="19">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="20"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="11"/>
+    </row>
+    <row r="9" spans="1:37" ht="85" x14ac:dyDescent="0.2">
+      <c r="A9" s="18">
+        <v>6</v>
+      </c>
+      <c r="B9" s="17">
+        <v>4</v>
+      </c>
+      <c r="C9" s="17">
+        <v>4</v>
+      </c>
+      <c r="D9" s="17">
+        <v>4</v>
+      </c>
+      <c r="E9" s="17">
+        <v>5</v>
+      </c>
+      <c r="F9" s="17">
+        <v>5</v>
+      </c>
+      <c r="G9" s="17">
+        <v>4</v>
+      </c>
+      <c r="H9" s="17">
+        <v>4</v>
+      </c>
+      <c r="I9" s="17">
+        <v>4</v>
+      </c>
+      <c r="J9" s="17">
+        <v>5</v>
+      </c>
+      <c r="K9" s="17">
+        <v>5</v>
+      </c>
+      <c r="L9" s="17">
+        <v>2</v>
+      </c>
+      <c r="M9" s="17">
+        <v>3</v>
+      </c>
+      <c r="N9" s="17">
+        <v>4</v>
+      </c>
+      <c r="O9" s="17">
+        <v>3</v>
+      </c>
+      <c r="P9" s="17">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="R9" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="S9" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="R7" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="S7" s="7"/>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A8" s="7">
-        <v>5</v>
-      </c>
-      <c r="B8" s="16">
-        <f>AVERAGE(B9:B10)</f>
-        <v>3.5</v>
-      </c>
-      <c r="C8" s="16">
-        <f t="shared" ref="C8:P8" si="0">AVERAGE(C9:C10)</f>
-        <v>3</v>
-      </c>
-      <c r="D8" s="16">
+      <c r="T9" s="10"/>
+      <c r="U9" s="10"/>
+      <c r="V9" s="10"/>
+      <c r="W9" s="10"/>
+      <c r="X9" s="10"/>
+      <c r="Y9" s="10"/>
+      <c r="Z9" s="10"/>
+      <c r="AA9" s="10"/>
+      <c r="AB9" s="10"/>
+      <c r="AC9" s="10"/>
+      <c r="AD9" s="10"/>
+      <c r="AE9" s="10"/>
+      <c r="AF9" s="10"/>
+      <c r="AG9" s="10"/>
+      <c r="AH9" s="10"/>
+      <c r="AI9" s="11"/>
+      <c r="AJ9" s="11"/>
+      <c r="AK9" s="11"/>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A10" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="19">
+        <f>AVERAGE(B4:B9)</f>
+        <v>4.083333333333333</v>
+      </c>
+      <c r="C10" s="19">
+        <f t="shared" ref="C10:P10" si="0">AVERAGE(C4:C9)</f>
+        <v>3.8333333333333335</v>
+      </c>
+      <c r="D10" s="19">
+        <f t="shared" si="0"/>
+        <v>4.083333333333333</v>
+      </c>
+      <c r="E10" s="19">
+        <f t="shared" si="0"/>
+        <v>4.166666666666667</v>
+      </c>
+      <c r="F10" s="19">
+        <f t="shared" si="0"/>
+        <v>4.416666666666667</v>
+      </c>
+      <c r="G10" s="19">
+        <f t="shared" si="0"/>
+        <v>4.083333333333333</v>
+      </c>
+      <c r="H10" s="19">
+        <f t="shared" si="0"/>
+        <v>4.416666666666667</v>
+      </c>
+      <c r="I10" s="19">
+        <f t="shared" si="0"/>
+        <v>3.9166666666666665</v>
+      </c>
+      <c r="J10" s="19">
+        <f t="shared" si="0"/>
+        <v>4.583333333333333</v>
+      </c>
+      <c r="K10" s="19">
+        <f t="shared" si="0"/>
+        <v>4.416666666666667</v>
+      </c>
+      <c r="L10" s="19">
+        <f t="shared" si="0"/>
+        <v>3.5833333333333335</v>
+      </c>
+      <c r="M10" s="19">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="E8" s="16">
+      <c r="N10" s="19">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="F8" s="16">
+        <v>3.9166666666666665</v>
+      </c>
+      <c r="O10" s="19">
         <f t="shared" si="0"/>
-        <v>2.5</v>
-      </c>
-      <c r="G8" s="16">
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="P10" s="19">
         <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
-      <c r="H8" s="16">
-        <f t="shared" si="0"/>
-        <v>4.5</v>
-      </c>
-      <c r="I8" s="16">
-        <f t="shared" si="0"/>
-        <v>2.5</v>
-      </c>
-      <c r="J8" s="16">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
-      <c r="K8" s="16">
-        <f t="shared" si="0"/>
-        <v>2.5</v>
-      </c>
-      <c r="L8" s="16">
-        <f t="shared" si="0"/>
-        <v>2.5</v>
-      </c>
-      <c r="M8" s="16">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="N8" s="16">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
-      <c r="O8" s="16">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="P8" s="16">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="Q8" s="17"/>
-      <c r="R8" s="17"/>
-      <c r="S8" s="17"/>
-    </row>
-    <row r="9" spans="1:19" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="9" t="s">
+        <v>3.8333333333333335</v>
+      </c>
+      <c r="Q10" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="R10" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="B9" s="10">
-        <v>5</v>
-      </c>
-      <c r="C9" s="10">
-        <v>4</v>
-      </c>
-      <c r="D9" s="10">
-        <v>4</v>
-      </c>
-      <c r="E9" s="10">
-        <v>3</v>
-      </c>
-      <c r="F9" s="10">
-        <v>3</v>
-      </c>
-      <c r="G9" s="10">
-        <v>4</v>
-      </c>
-      <c r="H9" s="10">
-        <v>5</v>
-      </c>
-      <c r="I9" s="10">
-        <v>3</v>
-      </c>
-      <c r="J9" s="10">
-        <v>4</v>
-      </c>
-      <c r="K9" s="10">
-        <v>3</v>
-      </c>
-      <c r="L9" s="10">
-        <v>3</v>
-      </c>
-      <c r="M9" s="10">
-        <v>3</v>
-      </c>
-      <c r="N9" s="10">
-        <v>4</v>
-      </c>
-      <c r="O9" s="10">
-        <v>2</v>
-      </c>
-      <c r="P9" s="10">
-        <v>2</v>
-      </c>
-      <c r="Q9" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="R9" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="S9" s="12" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="48" x14ac:dyDescent="0.2">
-      <c r="A10" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="B10" s="10">
-        <v>2</v>
-      </c>
-      <c r="C10" s="10">
-        <v>2</v>
-      </c>
-      <c r="D10" s="10">
-        <v>3</v>
-      </c>
-      <c r="E10" s="10">
-        <v>1</v>
-      </c>
-      <c r="F10" s="10">
-        <v>2</v>
-      </c>
-      <c r="G10" s="10">
-        <v>3</v>
-      </c>
-      <c r="H10" s="10">
-        <v>4</v>
-      </c>
-      <c r="I10" s="10">
-        <v>2</v>
-      </c>
-      <c r="J10" s="10">
-        <v>3</v>
-      </c>
-      <c r="K10" s="10">
-        <v>2</v>
-      </c>
-      <c r="L10" s="10">
-        <v>2</v>
-      </c>
-      <c r="M10" s="10">
-        <v>3</v>
-      </c>
-      <c r="N10" s="10">
-        <v>3</v>
-      </c>
-      <c r="O10" s="10">
-        <v>2</v>
-      </c>
-      <c r="P10" s="10">
-        <v>2</v>
-      </c>
-      <c r="Q10" s="13"/>
-      <c r="R10" s="13"/>
-      <c r="S10" s="14"/>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A11" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="B11" s="16">
-        <f>AVERAGE(B9:B10)</f>
-        <v>3.5</v>
-      </c>
-      <c r="C11" s="16">
-        <f t="shared" ref="C11:P11" si="1">AVERAGE(C9:C10)</f>
-        <v>3</v>
-      </c>
-      <c r="D11" s="16">
-        <f t="shared" si="1"/>
-        <v>3.5</v>
-      </c>
-      <c r="E11" s="16">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="F11" s="16">
-        <f t="shared" si="1"/>
-        <v>2.5</v>
-      </c>
-      <c r="G11" s="16">
-        <f t="shared" si="1"/>
-        <v>3.5</v>
-      </c>
-      <c r="H11" s="16">
-        <f t="shared" si="1"/>
-        <v>4.5</v>
-      </c>
-      <c r="I11" s="16">
-        <f t="shared" si="1"/>
-        <v>2.5</v>
-      </c>
-      <c r="J11" s="16">
-        <f t="shared" si="1"/>
-        <v>3.5</v>
-      </c>
-      <c r="K11" s="16">
-        <f t="shared" si="1"/>
-        <v>2.5</v>
-      </c>
-      <c r="L11" s="16">
-        <f t="shared" si="1"/>
-        <v>2.5</v>
-      </c>
-      <c r="M11" s="16">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="N11" s="16">
-        <f t="shared" si="1"/>
-        <v>3.5</v>
-      </c>
-      <c r="O11" s="16">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="P11" s="16">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="Q11" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="R11" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="S11" s="15"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="13"/>
-      <c r="R12" s="13"/>
-      <c r="S12" s="7"/>
+      <c r="S10" s="16"/>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="15"/>
+      <c r="R11" s="15"/>
+      <c r="S11" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="R9:R10"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="Q9:Q10"/>
-    <mergeCell ref="Q11:Q12"/>
-    <mergeCell ref="R11:R12"/>
+  <mergeCells count="2">
+    <mergeCell ref="Q10:Q11"/>
+    <mergeCell ref="R10:R11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1358,216 +1326,216 @@
   <sheetData>
     <row r="1" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="64" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="C20" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>73</v>
-      </c>
       <c r="C21" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
